--- a/artfynd/A 68630-2020 artfynd.xlsx
+++ b/artfynd/A 68630-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117577948</v>
+        <v>117577970</v>
       </c>
       <c r="B2" t="n">
-        <v>100931</v>
+        <v>94250</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>693</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Färgginst</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Genista tinctoria</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442981</v>
+        <v>442930</v>
       </c>
       <c r="R2" t="n">
-        <v>6520335</v>
+        <v>6520108</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117577970</v>
+        <v>117577948</v>
       </c>
       <c r="B3" t="n">
-        <v>94250</v>
+        <v>100931</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>693</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Färgginst</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Genista tinctoria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442930</v>
+        <v>442981</v>
       </c>
       <c r="R3" t="n">
-        <v>6520108</v>
+        <v>6520335</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 68630-2020 artfynd.xlsx
+++ b/artfynd/A 68630-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117577970</v>
+        <v>117577948</v>
       </c>
       <c r="B2" t="n">
-        <v>94250</v>
+        <v>100933</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>693</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Färgginst</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Genista tinctoria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442930</v>
+        <v>442981</v>
       </c>
       <c r="R2" t="n">
-        <v>6520108</v>
+        <v>6520335</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -775,17 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson, Jon Liljebäck, Ove Grönlund, Liselotte Larsson , Ewa Larsson, Ada  Arenander</t>
+          <t>Ada  Arenander, Ewa Larsson, Liselotte Larsson , Ove Grönlund, Jon Liljebäck, Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117577948</v>
+        <v>117577970</v>
       </c>
       <c r="B3" t="n">
-        <v>100931</v>
+        <v>94252</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>693</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Färgginst</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Genista tinctoria</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442981</v>
+        <v>442930</v>
       </c>
       <c r="R3" t="n">
-        <v>6520335</v>
+        <v>6520108</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
